--- a/bloodDonationTableControls.xlsx
+++ b/bloodDonationTableControls.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stell\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timnas/Documents/GitHub/BloodDonation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DAB3584-1ED6-4F35-95B8-94904E04ADA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74ED631A-3EC4-7745-AF25-5EFB95E7F428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DF095C4A-AA4C-DB45-A676-397A9CF76DAC}"/>
+    <workbookView xWindow="380" yWindow="2920" windowWidth="23260" windowHeight="12460" xr2:uid="{DF095C4A-AA4C-DB45-A676-397A9CF76DAC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="139">
   <si>
     <t>תאריך הניסוי</t>
   </si>
@@ -101,69 +101,12 @@
     <t>אישור על ידי מד"א</t>
   </si>
   <si>
-    <t>תחילת הקלטה בNH</t>
-  </si>
-  <si>
-    <t>Pulse1st</t>
-  </si>
-  <si>
-    <t>חיבור לדופק - שעה</t>
-  </si>
-  <si>
-    <t>Spo1st</t>
-  </si>
-  <si>
-    <t>חיבור לסטורציה - שעה</t>
-  </si>
-  <si>
-    <t>חיבור לל"ד - ערך ראשון</t>
-  </si>
-  <si>
-    <t>חיבור לל"ד - שעה</t>
-  </si>
-  <si>
-    <t>שעת מיקום על מיטה</t>
-  </si>
-  <si>
-    <t>שעת דקירה</t>
-  </si>
-  <si>
-    <t>סיום שאיבה</t>
-  </si>
-  <si>
     <t>Donation_amount_plus_bag</t>
   </si>
   <si>
     <t>Pure_Donation_Amount</t>
   </si>
   <si>
-    <t>המשך ניטור זמן סיום</t>
-  </si>
-  <si>
-    <t>מדידת נשימה 15 דקות במנוחה זמן סיום</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מדידה שניה - ל״ד </t>
-  </si>
-  <si>
-    <t>pulse2nd</t>
-  </si>
-  <si>
-    <t>spo2nd</t>
-  </si>
-  <si>
-    <t>מדידה שניה  - שעה</t>
-  </si>
-  <si>
-    <t>מילוי שאלון</t>
-  </si>
-  <si>
-    <t>הערות</t>
-  </si>
-  <si>
-    <t>שעה</t>
-  </si>
-  <si>
     <t>Weight</t>
   </si>
   <si>
@@ -194,9 +137,6 @@
     <t>האם את/ה מרגיש/ה חרדה או מתח? אם כן החל ממתי?</t>
   </si>
   <si>
-    <t>הערה כללית: תחילה צוין שמשקל שקית ריקה 87 גרם, אחר כך 157 גרם</t>
-  </si>
-  <si>
     <t>ד"ר נעה סופר סלעי</t>
   </si>
   <si>
@@ -206,9 +146,6 @@
     <t>128/73</t>
   </si>
   <si>
-    <t>הכנסת פקק</t>
-  </si>
-  <si>
     <t>קיבוע</t>
   </si>
   <si>
@@ -456,13 +393,73 @@
   </si>
   <si>
     <t>מעט, החל מתחילת-אמצע הניסוי</t>
+  </si>
+  <si>
+    <t>nh_recording_start</t>
+  </si>
+  <si>
+    <t>pulse_1st</t>
+  </si>
+  <si>
+    <t>pulse_connection_time</t>
+  </si>
+  <si>
+    <t>spo2_1st</t>
+  </si>
+  <si>
+    <t>spo2_connection_time</t>
+  </si>
+  <si>
+    <t>bp_1st</t>
+  </si>
+  <si>
+    <t>bp_connection_time</t>
+  </si>
+  <si>
+    <t>bed_placement_time</t>
+  </si>
+  <si>
+    <t>needle_time</t>
+  </si>
+  <si>
+    <t>flow_open_time</t>
+  </si>
+  <si>
+    <t>donation_end_time</t>
+  </si>
+  <si>
+    <t>monitoring_end_time</t>
+  </si>
+  <si>
+    <t>end_15min_after_recording</t>
+  </si>
+  <si>
+    <t>bp_2nd</t>
+  </si>
+  <si>
+    <t>pulse_2nd</t>
+  </si>
+  <si>
+    <t>spo2_2nd</t>
+  </si>
+  <si>
+    <t>second_measurement_time</t>
+  </si>
+  <si>
+    <t>questionnaire_completed</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>record_time</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -483,6 +480,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -531,13 +535,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -873,13 +878,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E86F6D9E-89CE-034C-B04D-D94C47E76EB5}">
   <dimension ref="A1:U42"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="51.8984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1">
         <v>108</v>
@@ -942,7 +947,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -986,28 +991,28 @@
         <v>45917</v>
       </c>
       <c r="O2" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="Q2" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="R2" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="S2" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="T2" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="U2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1051,28 +1056,28 @@
         <v>14</v>
       </c>
       <c r="O3" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="Q3" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="R3" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="S3" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="T3" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="U3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1137,72 +1142,72 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="G5" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="H5" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="I5" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="J5" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="K5" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="L5" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="M5" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="N5" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="O5" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="P5" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="Q5" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="R5" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="S5" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="T5" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="U5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
@@ -1267,74 +1272,74 @@
         <v>0.61805555555555558</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="G7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="I7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="J7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="K7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="L7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="M7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="N7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="O7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="P7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="Q7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="R7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="S7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="T7" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="U7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="B8" s="4">
         <v>0.44027777777777777</v>
@@ -1397,9 +1402,9 @@
         <v>0.62361111111111112</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="B9">
         <v>71</v>
@@ -1462,9 +1467,9 @@
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="B10" s="4">
         <v>0.44166666666666665</v>
@@ -1527,9 +1532,9 @@
         <v>0.62430555555555556</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="B11">
         <v>97</v>
@@ -1592,9 +1597,9 @@
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>25</v>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>123</v>
       </c>
       <c r="B12" s="4">
         <v>0.44166666666666665</v>
@@ -1657,74 +1662,74 @@
         <v>0.62430555555555556</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>124</v>
       </c>
       <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" t="s">
         <v>55</v>
       </c>
-      <c r="C13" t="s">
+      <c r="G13" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" t="s">
+        <v>62</v>
+      </c>
+      <c r="J13" t="s">
         <v>64</v>
       </c>
-      <c r="D13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" t="s">
-        <v>78</v>
-      </c>
-      <c r="H13" t="s">
-        <v>80</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="K13" t="s">
+        <v>66</v>
+      </c>
+      <c r="L13" t="s">
+        <v>68</v>
+      </c>
+      <c r="M13" t="s">
+        <v>73</v>
+      </c>
+      <c r="N13" t="s">
+        <v>75</v>
+      </c>
+      <c r="O13" t="s">
         <v>83</v>
       </c>
-      <c r="J13" t="s">
-        <v>85</v>
-      </c>
-      <c r="K13" t="s">
-        <v>87</v>
-      </c>
-      <c r="L13" t="s">
-        <v>89</v>
-      </c>
-      <c r="M13" t="s">
-        <v>94</v>
-      </c>
-      <c r="N13" t="s">
-        <v>96</v>
-      </c>
-      <c r="O13" t="s">
-        <v>104</v>
-      </c>
       <c r="P13" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="Q13" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="R13" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="S13" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="T13" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="U13" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>27</v>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
+        <v>125</v>
       </c>
       <c r="B14" s="4">
         <v>0.44166666666666665</v>
@@ -1787,9 +1792,9 @@
         <v>0.62430555555555556</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="B15" s="4">
         <v>0.4513888888888889</v>
@@ -1816,51 +1821,51 @@
         <v>0.55347222222222225</v>
       </c>
       <c r="J15" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="K15" s="4">
         <v>0.52361111111111114</v>
       </c>
       <c r="L15" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="M15" s="4">
         <v>0.53749999999999998</v>
       </c>
       <c r="N15" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="O15" s="4">
         <v>0.49583333333333335</v>
       </c>
       <c r="P15" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="Q15" s="4">
         <v>0.51111111111111107</v>
       </c>
       <c r="R15" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="T15" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="U15" s="4">
         <v>0.63472222222222219</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>29</v>
+        <v>127</v>
       </c>
       <c r="B16" s="4">
         <v>0.45277777777777778</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="D16" s="4">
         <v>0.46111111111111114</v>
@@ -1887,7 +1892,7 @@
         <v>0.52430555555555558</v>
       </c>
       <c r="L16" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M16" s="4">
         <v>0.53749999999999998</v>
@@ -1899,7 +1904,7 @@
         <v>0.49722222222222223</v>
       </c>
       <c r="P16" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="Q16" s="4">
         <v>0.51458333333333328</v>
@@ -1917,9 +1922,9 @@
         <v>0.63611111111111107</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="B17" s="4">
         <v>0.45277777777777778</v>
@@ -1931,69 +1936,69 @@
         <v>0.46180555555555558</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="G17" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="H17" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="I17" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="J17" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="K17" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="L17" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="M17" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="N17" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="O17" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="P17" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="Q17" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="R17" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="S17" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="T17" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="U17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B18" s="4">
         <v>0.45416666666666666</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="E18" s="4">
         <v>0.49236111111111114</v>
@@ -2014,16 +2019,16 @@
         <v>0.55902777777777779</v>
       </c>
       <c r="K18" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="L18" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="M18" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="O18" s="4">
         <v>0.49791666666666667</v>
@@ -2035,21 +2040,21 @@
         <v>0.51597222222222228</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="U18" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>30</v>
+        <v>129</v>
       </c>
       <c r="B19" s="4">
         <v>0.46388888888888891</v>
@@ -2094,7 +2099,7 @@
         <v>0.5083333333333333</v>
       </c>
       <c r="P19" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="Q19" s="4">
         <v>0.52430555555555558</v>
@@ -2112,9 +2117,9 @@
         <v>0.64722222222222225</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2177,9 +2182,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2242,9 +2247,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="B22" s="4">
         <v>0.46458333333333335</v>
@@ -2289,24 +2294,24 @@
         <v>0.51041666666666663</v>
       </c>
       <c r="P22" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="Q22" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="S22" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="T22" s="4">
         <v>0.63958333333333328</v>
       </c>
       <c r="U22" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="B23" s="4">
         <v>0.47499999999999998</v>
@@ -2351,13 +2356,13 @@
         <v>0.52013888888888893</v>
       </c>
       <c r="P23" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="Q23" s="4">
         <v>0.53611111111111109</v>
       </c>
       <c r="S23" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="T23" s="4">
         <v>0.65</v>
@@ -2366,71 +2371,71 @@
         <v>0.65763888888888888</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>35</v>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A24" s="6" t="s">
+        <v>132</v>
       </c>
       <c r="B24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" t="s">
+        <v>52</v>
+      </c>
+      <c r="F24" t="s">
+        <v>56</v>
+      </c>
+      <c r="G24" t="s">
         <v>58</v>
       </c>
-      <c r="C24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="H24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I24" t="s">
+        <v>63</v>
+      </c>
+      <c r="J24" t="s">
+        <v>65</v>
+      </c>
+      <c r="K24" t="s">
+        <v>67</v>
+      </c>
+      <c r="L24" t="s">
         <v>70</v>
       </c>
-      <c r="E24" t="s">
-        <v>73</v>
-      </c>
-      <c r="F24" t="s">
-        <v>77</v>
-      </c>
-      <c r="G24" t="s">
-        <v>79</v>
-      </c>
-      <c r="H24" t="s">
-        <v>81</v>
-      </c>
-      <c r="I24" t="s">
-        <v>84</v>
-      </c>
-      <c r="J24" t="s">
-        <v>86</v>
-      </c>
-      <c r="K24" t="s">
-        <v>88</v>
-      </c>
-      <c r="L24" t="s">
-        <v>91</v>
-      </c>
       <c r="M24" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="N24" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="P24" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="Q24" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="S24" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="T24" t="s">
+        <v>112</v>
+      </c>
+      <c r="U24" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="U24" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="B25">
         <v>80</v>
@@ -2490,9 +2495,9 @@
         <v>93</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="B26">
         <v>98</v>
@@ -2552,9 +2557,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>38</v>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="B27" s="4">
         <v>0.46597222222222223</v>
@@ -2584,7 +2589,7 @@
         <v>0.57361111111111107</v>
       </c>
       <c r="K27" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="L27" s="4">
         <v>0.55625000000000002</v>
@@ -2614,136 +2619,136 @@
         <v>0.65138888888888891</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>39</v>
+        <v>136</v>
       </c>
       <c r="B28" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D28" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="F28" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="G28" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="H28" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="I28" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="J28" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="K28" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="L28" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="M28" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="N28" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="O28" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="P28" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="Q28" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="S28" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="T28" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="U28" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>40</v>
+        <v>137</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="D29" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F29" t="s">
+        <v>38</v>
+      </c>
+      <c r="G29" t="s">
+        <v>38</v>
+      </c>
+      <c r="H29" t="s">
+        <v>38</v>
+      </c>
+      <c r="I29" t="s">
+        <v>38</v>
+      </c>
+      <c r="J29" t="s">
+        <v>38</v>
+      </c>
+      <c r="K29" t="s">
+        <v>38</v>
+      </c>
+      <c r="L29" t="s">
         <v>71</v>
       </c>
-      <c r="E29" t="s">
-        <v>74</v>
-      </c>
-      <c r="F29" t="s">
-        <v>59</v>
-      </c>
-      <c r="G29" t="s">
-        <v>59</v>
-      </c>
-      <c r="H29" t="s">
-        <v>59</v>
-      </c>
-      <c r="I29" t="s">
-        <v>59</v>
-      </c>
-      <c r="J29" t="s">
-        <v>59</v>
-      </c>
-      <c r="K29" t="s">
-        <v>59</v>
-      </c>
-      <c r="L29" t="s">
-        <v>92</v>
-      </c>
       <c r="M29" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="N29" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="O29" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="P29" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="Q29" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="R29" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="S29" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="T29" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="U29" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
         <v>138</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="B30" s="4">
         <v>0.46736111111111112</v>
@@ -2800,9 +2805,9 @@
         <v>0.65277777777777779</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="B31">
         <v>73</v>
@@ -2865,9 +2870,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="B32">
         <v>170</v>
@@ -2930,9 +2935,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B33">
         <v>20</v>
@@ -2995,400 +3000,398 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" t="s">
+        <v>27</v>
+      </c>
+      <c r="G34" t="s">
+        <v>27</v>
+      </c>
+      <c r="H34" t="s">
+        <v>27</v>
+      </c>
+      <c r="I34" t="s">
+        <v>27</v>
+      </c>
+      <c r="J34" t="s">
+        <v>27</v>
+      </c>
+      <c r="K34" t="s">
+        <v>27</v>
+      </c>
+      <c r="L34" t="s">
+        <v>27</v>
+      </c>
+      <c r="M34" t="s">
+        <v>27</v>
+      </c>
+      <c r="N34" t="s">
+        <v>27</v>
+      </c>
+      <c r="O34" t="s">
+        <v>84</v>
+      </c>
+      <c r="P34" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>84</v>
+      </c>
+      <c r="R34" t="s">
+        <v>84</v>
+      </c>
+      <c r="S34" t="s">
+        <v>84</v>
+      </c>
+      <c r="T34" t="s">
+        <v>84</v>
+      </c>
+      <c r="U34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" t="s">
         <v>46</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D35" t="s">
         <v>46</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E35" t="s">
         <v>46</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F35" t="s">
         <v>46</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G35" t="s">
+        <v>39</v>
+      </c>
+      <c r="H35" t="s">
         <v>46</v>
       </c>
-      <c r="G34" t="s">
+      <c r="I35" t="s">
         <v>46</v>
       </c>
-      <c r="H34" t="s">
+      <c r="J35" t="s">
         <v>46</v>
       </c>
-      <c r="I34" t="s">
+      <c r="K35" t="s">
         <v>46</v>
       </c>
-      <c r="J34" t="s">
+      <c r="L35" t="s">
+        <v>39</v>
+      </c>
+      <c r="M35" t="s">
+        <v>39</v>
+      </c>
+      <c r="N35" t="s">
+        <v>39</v>
+      </c>
+      <c r="O35" t="s">
         <v>46</v>
       </c>
-      <c r="K34" t="s">
+      <c r="P35" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>39</v>
+      </c>
+      <c r="R35" t="s">
+        <v>103</v>
+      </c>
+      <c r="S35" t="s">
         <v>46</v>
       </c>
-      <c r="L34" t="s">
+      <c r="T35" t="s">
         <v>46</v>
       </c>
-      <c r="M34" t="s">
+      <c r="U35" t="s">
         <v>46</v>
       </c>
-      <c r="N34" t="s">
-        <v>46</v>
-      </c>
-      <c r="O34" t="s">
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" t="s">
+        <v>41</v>
+      </c>
+      <c r="F36" t="s">
+        <v>41</v>
+      </c>
+      <c r="G36" t="s">
+        <v>41</v>
+      </c>
+      <c r="H36" t="s">
+        <v>41</v>
+      </c>
+      <c r="I36" t="s">
+        <v>41</v>
+      </c>
+      <c r="J36" t="s">
+        <v>41</v>
+      </c>
+      <c r="K36" t="s">
+        <v>41</v>
+      </c>
+      <c r="L36" t="s">
+        <v>72</v>
+      </c>
+      <c r="M36" t="s">
+        <v>72</v>
+      </c>
+      <c r="N36" t="s">
+        <v>78</v>
+      </c>
+      <c r="O36" t="s">
+        <v>41</v>
+      </c>
+      <c r="P36" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>98</v>
+      </c>
+      <c r="R36" t="s">
+        <v>40</v>
+      </c>
+      <c r="S36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T36" t="s">
+        <v>41</v>
+      </c>
+      <c r="U36" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" t="s">
+        <v>41</v>
+      </c>
+      <c r="E37" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" t="s">
+        <v>41</v>
+      </c>
+      <c r="G37" t="s">
+        <v>40</v>
+      </c>
+      <c r="H37" t="s">
+        <v>61</v>
+      </c>
+      <c r="I37" t="s">
+        <v>41</v>
+      </c>
+      <c r="J37" t="s">
+        <v>41</v>
+      </c>
+      <c r="K37" t="s">
+        <v>61</v>
+      </c>
+      <c r="L37" t="s">
+        <v>41</v>
+      </c>
+      <c r="M37" t="s">
+        <v>40</v>
+      </c>
+      <c r="N37" t="s">
+        <v>41</v>
+      </c>
+      <c r="O37" t="s">
+        <v>41</v>
+      </c>
+      <c r="P37" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>41</v>
+      </c>
+      <c r="R37" t="s">
+        <v>104</v>
+      </c>
+      <c r="S37" t="s">
+        <v>41</v>
+      </c>
+      <c r="T37" t="s">
+        <v>61</v>
+      </c>
+      <c r="U37" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" t="s">
+        <v>41</v>
+      </c>
+      <c r="F38" t="s">
+        <v>41</v>
+      </c>
+      <c r="G38" t="s">
+        <v>41</v>
+      </c>
+      <c r="H38" t="s">
+        <v>41</v>
+      </c>
+      <c r="I38" t="s">
+        <v>41</v>
+      </c>
+      <c r="J38" t="s">
+        <v>41</v>
+      </c>
+      <c r="K38" t="s">
+        <v>41</v>
+      </c>
+      <c r="L38" t="s">
+        <v>41</v>
+      </c>
+      <c r="M38" t="s">
+        <v>41</v>
+      </c>
+      <c r="N38" t="s">
+        <v>79</v>
+      </c>
+      <c r="O38" t="s">
+        <v>41</v>
+      </c>
+      <c r="P38" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>41</v>
+      </c>
+      <c r="R38" t="s">
+        <v>79</v>
+      </c>
+      <c r="S38" t="s">
+        <v>41</v>
+      </c>
+      <c r="T38" t="s">
+        <v>41</v>
+      </c>
+      <c r="U38" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" t="s">
+        <v>41</v>
+      </c>
+      <c r="F39" t="s">
+        <v>41</v>
+      </c>
+      <c r="G39" t="s">
+        <v>54</v>
+      </c>
+      <c r="H39" t="s">
+        <v>41</v>
+      </c>
+      <c r="I39" t="s">
+        <v>41</v>
+      </c>
+      <c r="J39" t="s">
+        <v>41</v>
+      </c>
+      <c r="K39" t="s">
+        <v>41</v>
+      </c>
+      <c r="L39" t="s">
+        <v>41</v>
+      </c>
+      <c r="M39" t="s">
+        <v>41</v>
+      </c>
+      <c r="N39" t="s">
+        <v>41</v>
+      </c>
+      <c r="O39" t="s">
+        <v>41</v>
+      </c>
+      <c r="P39" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>99</v>
+      </c>
+      <c r="R39" t="s">
         <v>105</v>
       </c>
-      <c r="P34" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>105</v>
-      </c>
-      <c r="R34" t="s">
-        <v>105</v>
-      </c>
-      <c r="S34" t="s">
-        <v>105</v>
-      </c>
-      <c r="T34" t="s">
-        <v>105</v>
-      </c>
-      <c r="U34" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B35" t="s">
-        <v>60</v>
-      </c>
-      <c r="C35" t="s">
-        <v>67</v>
-      </c>
-      <c r="D35" t="s">
-        <v>67</v>
-      </c>
-      <c r="E35" t="s">
-        <v>67</v>
-      </c>
-      <c r="F35" t="s">
-        <v>67</v>
-      </c>
-      <c r="G35" t="s">
-        <v>60</v>
-      </c>
-      <c r="H35" t="s">
-        <v>67</v>
-      </c>
-      <c r="I35" t="s">
-        <v>67</v>
-      </c>
-      <c r="J35" t="s">
-        <v>67</v>
-      </c>
-      <c r="K35" t="s">
-        <v>67</v>
-      </c>
-      <c r="L35" t="s">
-        <v>60</v>
-      </c>
-      <c r="M35" t="s">
-        <v>60</v>
-      </c>
-      <c r="N35" t="s">
-        <v>60</v>
-      </c>
-      <c r="O35" t="s">
-        <v>67</v>
-      </c>
-      <c r="P35" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>60</v>
-      </c>
-      <c r="R35" t="s">
-        <v>124</v>
-      </c>
-      <c r="S35" t="s">
-        <v>67</v>
-      </c>
-      <c r="T35" t="s">
-        <v>67</v>
-      </c>
-      <c r="U35" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36" t="s">
-        <v>61</v>
-      </c>
-      <c r="C36" t="s">
-        <v>62</v>
-      </c>
-      <c r="D36" t="s">
-        <v>62</v>
-      </c>
-      <c r="E36" t="s">
-        <v>62</v>
-      </c>
-      <c r="F36" t="s">
-        <v>62</v>
-      </c>
-      <c r="G36" t="s">
-        <v>62</v>
-      </c>
-      <c r="H36" t="s">
-        <v>62</v>
-      </c>
-      <c r="I36" t="s">
-        <v>62</v>
-      </c>
-      <c r="J36" t="s">
-        <v>62</v>
-      </c>
-      <c r="K36" t="s">
-        <v>62</v>
-      </c>
-      <c r="L36" t="s">
-        <v>93</v>
-      </c>
-      <c r="M36" t="s">
-        <v>93</v>
-      </c>
-      <c r="N36" t="s">
-        <v>99</v>
-      </c>
-      <c r="O36" t="s">
-        <v>62</v>
-      </c>
-      <c r="P36" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>119</v>
-      </c>
-      <c r="R36" t="s">
-        <v>61</v>
-      </c>
-      <c r="S36" t="s">
-        <v>62</v>
-      </c>
-      <c r="T36" t="s">
-        <v>62</v>
-      </c>
-      <c r="U36" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B37" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" t="s">
-        <v>62</v>
-      </c>
-      <c r="D37" t="s">
-        <v>62</v>
-      </c>
-      <c r="E37" t="s">
-        <v>75</v>
-      </c>
-      <c r="F37" t="s">
-        <v>62</v>
-      </c>
-      <c r="G37" t="s">
-        <v>61</v>
-      </c>
-      <c r="H37" t="s">
-        <v>82</v>
-      </c>
-      <c r="I37" t="s">
-        <v>62</v>
-      </c>
-      <c r="J37" t="s">
-        <v>62</v>
-      </c>
-      <c r="K37" t="s">
-        <v>82</v>
-      </c>
-      <c r="L37" t="s">
-        <v>62</v>
-      </c>
-      <c r="M37" t="s">
-        <v>61</v>
-      </c>
-      <c r="N37" t="s">
-        <v>62</v>
-      </c>
-      <c r="O37" t="s">
-        <v>62</v>
-      </c>
-      <c r="P37" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>62</v>
-      </c>
-      <c r="R37" t="s">
-        <v>125</v>
-      </c>
-      <c r="S37" t="s">
-        <v>62</v>
-      </c>
-      <c r="T37" t="s">
-        <v>82</v>
-      </c>
-      <c r="U37" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B38" t="s">
-        <v>62</v>
-      </c>
-      <c r="C38" t="s">
-        <v>62</v>
-      </c>
-      <c r="D38" t="s">
-        <v>62</v>
-      </c>
-      <c r="E38" t="s">
-        <v>62</v>
-      </c>
-      <c r="F38" t="s">
-        <v>62</v>
-      </c>
-      <c r="G38" t="s">
-        <v>62</v>
-      </c>
-      <c r="H38" t="s">
-        <v>62</v>
-      </c>
-      <c r="I38" t="s">
-        <v>62</v>
-      </c>
-      <c r="J38" t="s">
-        <v>62</v>
-      </c>
-      <c r="K38" t="s">
-        <v>62</v>
-      </c>
-      <c r="L38" t="s">
-        <v>62</v>
-      </c>
-      <c r="M38" t="s">
-        <v>62</v>
-      </c>
-      <c r="N38" t="s">
-        <v>100</v>
-      </c>
-      <c r="O38" t="s">
-        <v>62</v>
-      </c>
-      <c r="P38" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>62</v>
-      </c>
-      <c r="R38" t="s">
-        <v>100</v>
-      </c>
-      <c r="S38" t="s">
-        <v>62</v>
-      </c>
-      <c r="T38" t="s">
-        <v>62</v>
-      </c>
-      <c r="U38" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B39" t="s">
-        <v>62</v>
-      </c>
-      <c r="C39" t="s">
-        <v>62</v>
-      </c>
-      <c r="D39" t="s">
-        <v>62</v>
-      </c>
-      <c r="E39" t="s">
-        <v>62</v>
-      </c>
-      <c r="F39" t="s">
-        <v>62</v>
-      </c>
-      <c r="G39" t="s">
-        <v>75</v>
-      </c>
-      <c r="H39" t="s">
-        <v>62</v>
-      </c>
-      <c r="I39" t="s">
-        <v>62</v>
-      </c>
-      <c r="J39" t="s">
-        <v>62</v>
-      </c>
-      <c r="K39" t="s">
-        <v>62</v>
-      </c>
-      <c r="L39" t="s">
-        <v>62</v>
-      </c>
-      <c r="M39" t="s">
-        <v>62</v>
-      </c>
-      <c r="N39" t="s">
-        <v>62</v>
-      </c>
-      <c r="O39" t="s">
-        <v>62</v>
-      </c>
-      <c r="P39" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>120</v>
-      </c>
-      <c r="R39" t="s">
-        <v>126</v>
-      </c>
       <c r="S39" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="T39" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="U39" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>52</v>
-      </c>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A42" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
